--- a/excel/PEDIDOS_2026.xlsx
+++ b/excel/PEDIDOS_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIOS\ADM05\Documents\dashboard_tv\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C68D52-3A6E-422C-930C-EC12CF46D131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA50517A-B7FA-4ECA-A011-3A9D925218D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{C1828F10-D84A-418A-AAF0-1B51BFAF300A}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="23" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4066" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4185" uniqueCount="247">
   <si>
     <t>Empresa/Filial</t>
   </si>
@@ -768,6 +768,12 @@
   </si>
   <si>
     <t>SC BALNEARIO CAMBORIU</t>
+  </si>
+  <si>
+    <t>JUNO IMPORTADORA</t>
+  </si>
+  <si>
+    <t>BUP BABY</t>
   </si>
 </sst>
 </file>
@@ -91973,7 +91979,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{02CBC691-8FE5-4117-AD29-0522370051A7}" name="Tabela dinâmica1" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{02CBC691-8FE5-4117-AD29-0522370051A7}" name="Tabela dinâmica1" cacheId="23" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="47">
     <pivotField showAll="0"/>
@@ -115842,91 +115848,675 @@
         <v>53</v>
       </c>
     </row>
-    <row r="241" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B241" s="1"/>
-      <c r="E241" s="2"/>
-      <c r="H241" s="3"/>
-      <c r="I241" s="3"/>
-      <c r="K241" s="3"/>
-      <c r="L241" s="3"/>
-      <c r="X241" s="4"/>
-      <c r="Z241" s="3"/>
-      <c r="AB241" s="3"/>
-      <c r="AE241" s="3"/>
-      <c r="AK241" s="5"/>
-    </row>
-    <row r="242" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B242" s="1"/>
-      <c r="E242" s="2"/>
-      <c r="H242" s="3"/>
-      <c r="I242" s="3"/>
-      <c r="K242" s="3"/>
-      <c r="L242" s="3"/>
-      <c r="X242" s="4"/>
+    <row r="241" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>47</v>
+      </c>
+      <c r="B241" s="1">
+        <v>38586</v>
+      </c>
+      <c r="C241" t="s">
+        <v>48</v>
+      </c>
+      <c r="D241" t="s">
+        <v>49</v>
+      </c>
+      <c r="E241" s="2">
+        <v>46076</v>
+      </c>
+      <c r="F241" t="s">
+        <v>175</v>
+      </c>
+      <c r="G241" t="s">
+        <v>61</v>
+      </c>
+      <c r="H241" s="3">
+        <v>8950</v>
+      </c>
+      <c r="I241" s="3">
+        <v>8950</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241" s="3">
+        <v>10292.5</v>
+      </c>
+      <c r="L241" s="3">
+        <v>866.9</v>
+      </c>
+      <c r="M241" s="3">
+        <v>553.08000000000004</v>
+      </c>
+      <c r="N241" t="s">
+        <v>50</v>
+      </c>
+      <c r="O241" t="s">
+        <v>51</v>
+      </c>
+      <c r="P241" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>51</v>
+      </c>
+      <c r="R241" t="s">
+        <v>52</v>
+      </c>
+      <c r="S241" t="s">
+        <v>52</v>
+      </c>
+      <c r="T241" t="s">
+        <v>53</v>
+      </c>
+      <c r="U241">
+        <v>126</v>
+      </c>
+      <c r="V241" t="s">
+        <v>54</v>
+      </c>
+      <c r="W241" t="s">
+        <v>176</v>
+      </c>
+      <c r="X241" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y241" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z241" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA241">
+        <v>0</v>
+      </c>
+      <c r="AB241" s="3">
+        <v>866.9</v>
+      </c>
+      <c r="AC241">
+        <v>0</v>
+      </c>
+      <c r="AD241">
+        <v>0</v>
+      </c>
+      <c r="AE241" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF241" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG241" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI241" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ241" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK241" s="5">
+        <v>46076.34578703704</v>
+      </c>
+      <c r="AO241" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP241">
+        <v>0</v>
+      </c>
+      <c r="AR241" t="s">
+        <v>52</v>
+      </c>
+      <c r="AS241" t="s">
+        <v>52</v>
+      </c>
+      <c r="AT241">
+        <v>1269</v>
+      </c>
+      <c r="AU241" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="242" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>72</v>
+      </c>
+      <c r="B242" s="1">
+        <v>38587</v>
+      </c>
+      <c r="C242" t="s">
+        <v>48</v>
+      </c>
+      <c r="D242" t="s">
+        <v>49</v>
+      </c>
+      <c r="E242" s="2">
+        <v>46076</v>
+      </c>
+      <c r="F242" t="s">
+        <v>245</v>
+      </c>
+      <c r="G242" t="s">
+        <v>63</v>
+      </c>
+      <c r="H242" s="3">
+        <v>52725</v>
+      </c>
+      <c r="I242" s="3">
+        <v>52725</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242" s="3">
+        <v>52725</v>
+      </c>
+      <c r="L242" s="3">
+        <v>8812.5</v>
+      </c>
+      <c r="M242" s="3">
+        <v>5243.45</v>
+      </c>
+      <c r="N242" t="s">
+        <v>50</v>
+      </c>
+      <c r="O242" t="s">
+        <v>51</v>
+      </c>
+      <c r="P242" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>51</v>
+      </c>
+      <c r="R242" t="s">
+        <v>52</v>
+      </c>
+      <c r="S242" t="s">
+        <v>52</v>
+      </c>
+      <c r="T242" t="s">
+        <v>53</v>
+      </c>
+      <c r="U242">
+        <v>126</v>
+      </c>
+      <c r="V242" t="s">
+        <v>54</v>
+      </c>
+      <c r="W242" t="s">
+        <v>91</v>
+      </c>
+      <c r="X242" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y242" t="s">
+        <v>59</v>
+      </c>
       <c r="Z242" s="3"/>
       <c r="AE242" s="3"/>
       <c r="AK242" s="5"/>
     </row>
-    <row r="243" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B243" s="1"/>
-      <c r="E243" s="2"/>
-      <c r="H243" s="3"/>
-      <c r="I243" s="3"/>
-      <c r="K243" s="3"/>
-      <c r="L243" s="3"/>
+    <row r="243" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>60</v>
+      </c>
+      <c r="B243" s="1">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243" s="3">
+        <v>8812.5</v>
+      </c>
+      <c r="E243" s="2">
+        <v>0</v>
+      </c>
+      <c r="F243">
+        <v>0</v>
+      </c>
+      <c r="G243" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K243" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L243" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M243" s="3">
+        <v>46076.356805555559</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>52</v>
+      </c>
+      <c r="R243">
+        <v>0</v>
+      </c>
+      <c r="T243" t="s">
+        <v>52</v>
+      </c>
+      <c r="U243" t="s">
+        <v>52</v>
+      </c>
+      <c r="V243">
+        <v>8701</v>
+      </c>
+      <c r="W243" t="s">
+        <v>53</v>
+      </c>
       <c r="X243" s="4"/>
       <c r="Z243" s="3"/>
       <c r="AD243" s="3"/>
       <c r="AE243" s="3"/>
       <c r="AK243" s="5"/>
     </row>
-    <row r="244" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B244" s="1"/>
-      <c r="E244" s="2"/>
-      <c r="H244" s="3"/>
-      <c r="I244" s="3"/>
-      <c r="K244" s="3"/>
-      <c r="L244" s="3"/>
-      <c r="X244" s="4"/>
-      <c r="AE244" s="3"/>
-      <c r="AK244" s="5"/>
-    </row>
-    <row r="245" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B245" s="1"/>
-      <c r="D245" s="3"/>
-      <c r="E245" s="2"/>
-      <c r="G245" s="3"/>
-      <c r="H245" s="3"/>
-      <c r="I245" s="3"/>
-      <c r="K245" s="3"/>
-      <c r="L245" s="3"/>
-      <c r="X245" s="4"/>
-      <c r="Z245" s="3"/>
-      <c r="AE245" s="3"/>
-      <c r="AK245" s="5"/>
-    </row>
-    <row r="246" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B246" s="1"/>
-      <c r="E246" s="2"/>
-      <c r="H246" s="3"/>
-      <c r="I246" s="3"/>
-      <c r="K246" s="3"/>
-      <c r="X246" s="4"/>
+    <row r="244" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>82</v>
+      </c>
+      <c r="B244" s="1">
+        <v>38588</v>
+      </c>
+      <c r="C244" t="s">
+        <v>48</v>
+      </c>
+      <c r="D244" t="s">
+        <v>49</v>
+      </c>
+      <c r="E244" s="2">
+        <v>46076</v>
+      </c>
+      <c r="F244" t="s">
+        <v>246</v>
+      </c>
+      <c r="G244" t="s">
+        <v>63</v>
+      </c>
+      <c r="H244" s="3">
+        <v>4788</v>
+      </c>
+      <c r="I244" s="3">
+        <v>4788</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244" s="3">
+        <v>4788</v>
+      </c>
+      <c r="L244" s="3">
+        <v>831</v>
+      </c>
+      <c r="M244" s="3">
+        <v>477.83</v>
+      </c>
+      <c r="N244" t="s">
+        <v>50</v>
+      </c>
+      <c r="O244" t="s">
+        <v>51</v>
+      </c>
+      <c r="P244" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>51</v>
+      </c>
+      <c r="R244" t="s">
+        <v>52</v>
+      </c>
+      <c r="S244" t="s">
+        <v>52</v>
+      </c>
+      <c r="T244" t="s">
+        <v>53</v>
+      </c>
+      <c r="U244">
+        <v>126</v>
+      </c>
+      <c r="V244" t="s">
+        <v>54</v>
+      </c>
+      <c r="W244" t="s">
+        <v>66</v>
+      </c>
+      <c r="X244" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y244" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z244">
+        <v>0</v>
+      </c>
+      <c r="AA244">
+        <v>0</v>
+      </c>
+      <c r="AB244">
+        <v>831</v>
+      </c>
+      <c r="AC244">
+        <v>0</v>
+      </c>
+      <c r="AD244">
+        <v>0</v>
+      </c>
+      <c r="AE244" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF244" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG244" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI244" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ244" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK244" s="5">
+        <v>46076.378310185188</v>
+      </c>
+      <c r="AO244" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP244">
+        <v>0</v>
+      </c>
+      <c r="AR244" t="s">
+        <v>52</v>
+      </c>
+      <c r="AS244" t="s">
+        <v>52</v>
+      </c>
+      <c r="AT244">
+        <v>5152</v>
+      </c>
+      <c r="AU244" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="245" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>82</v>
+      </c>
+      <c r="B245" s="1">
+        <v>38590</v>
+      </c>
+      <c r="C245" t="s">
+        <v>48</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E245" s="2">
+        <v>46076</v>
+      </c>
+      <c r="F245" t="s">
+        <v>215</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H245" s="3">
+        <v>14290</v>
+      </c>
+      <c r="I245" s="3">
+        <v>14290</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245" s="3">
+        <v>14290</v>
+      </c>
+      <c r="L245" s="3">
+        <v>2294</v>
+      </c>
+      <c r="M245" s="3">
+        <v>1364.93</v>
+      </c>
+      <c r="N245" t="s">
+        <v>50</v>
+      </c>
+      <c r="O245" t="s">
+        <v>51</v>
+      </c>
+      <c r="P245" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>51</v>
+      </c>
+      <c r="R245" t="s">
+        <v>52</v>
+      </c>
+      <c r="S245" t="s">
+        <v>52</v>
+      </c>
+      <c r="T245" t="s">
+        <v>53</v>
+      </c>
+      <c r="U245">
+        <v>126</v>
+      </c>
+      <c r="V245" t="s">
+        <v>54</v>
+      </c>
+      <c r="W245" t="s">
+        <v>106</v>
+      </c>
+      <c r="X245" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y245" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z245" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA245">
+        <v>0</v>
+      </c>
+      <c r="AB245" s="3">
+        <v>2294</v>
+      </c>
+      <c r="AC245">
+        <v>0</v>
+      </c>
+      <c r="AD245">
+        <v>0</v>
+      </c>
+      <c r="AE245" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF245" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG245" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH245" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI245" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ245" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK245" s="5">
+        <v>46076.476377314815</v>
+      </c>
+      <c r="AO245" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP245">
+        <v>0</v>
+      </c>
+      <c r="AR245" t="s">
+        <v>52</v>
+      </c>
+      <c r="AS245" t="s">
+        <v>52</v>
+      </c>
+      <c r="AT245">
+        <v>5486</v>
+      </c>
+      <c r="AU245" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="246" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>47</v>
+      </c>
+      <c r="B246" s="1">
+        <v>38591</v>
+      </c>
+      <c r="C246" t="s">
+        <v>48</v>
+      </c>
+      <c r="D246" t="s">
+        <v>49</v>
+      </c>
+      <c r="E246" s="2">
+        <v>46076</v>
+      </c>
+      <c r="F246" t="s">
+        <v>111</v>
+      </c>
+      <c r="G246" t="s">
+        <v>76</v>
+      </c>
+      <c r="H246" s="3">
+        <v>539.20000000000005</v>
+      </c>
+      <c r="I246" s="3">
+        <v>539.20000000000005</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246" s="3">
+        <v>620.08000000000004</v>
+      </c>
+      <c r="L246">
+        <v>82.04</v>
+      </c>
+      <c r="M246" s="3">
+        <v>52.34</v>
+      </c>
+      <c r="N246" t="s">
+        <v>50</v>
+      </c>
+      <c r="O246" t="s">
+        <v>51</v>
+      </c>
+      <c r="P246" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>51</v>
+      </c>
+      <c r="R246" t="s">
+        <v>52</v>
+      </c>
+      <c r="S246" t="s">
+        <v>52</v>
+      </c>
+      <c r="T246" t="s">
+        <v>53</v>
+      </c>
+      <c r="U246">
+        <v>126</v>
+      </c>
+      <c r="V246" t="s">
+        <v>54</v>
+      </c>
+      <c r="W246" t="s">
+        <v>81</v>
+      </c>
+      <c r="X246" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y246" t="s">
+        <v>59</v>
+      </c>
       <c r="AK246" s="5"/>
     </row>
-    <row r="247" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B247" s="1"/>
-      <c r="E247" s="2"/>
-      <c r="G247" s="3"/>
-      <c r="H247" s="3"/>
-      <c r="I247" s="3"/>
-      <c r="K247" s="3"/>
-      <c r="L247" s="3"/>
+    <row r="247" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>60</v>
+      </c>
+      <c r="B247" s="1">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>82.04</v>
+      </c>
+      <c r="E247" s="2">
+        <v>0</v>
+      </c>
+      <c r="F247">
+        <v>0</v>
+      </c>
+      <c r="G247" s="3">
+        <v>40</v>
+      </c>
+      <c r="H247" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J247" t="s">
+        <v>112</v>
+      </c>
+      <c r="K247" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L247" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M247" s="3">
+        <v>46076.49009259259</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>52</v>
+      </c>
+      <c r="R247">
+        <v>0</v>
+      </c>
+      <c r="T247" t="s">
+        <v>52</v>
+      </c>
+      <c r="U247" t="s">
+        <v>52</v>
+      </c>
+      <c r="V247">
+        <v>8478</v>
+      </c>
+      <c r="W247" t="s">
+        <v>53</v>
+      </c>
       <c r="X247" s="4"/>
       <c r="AE247" s="3"/>
       <c r="AK247" s="5"/>
     </row>
-    <row r="248" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B248" s="1"/>
       <c r="E248" s="2"/>
       <c r="H248" s="3"/>
@@ -115935,7 +116525,7 @@
       <c r="X248" s="4"/>
       <c r="AK248" s="5"/>
     </row>
-    <row r="249" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B249" s="1"/>
       <c r="E249" s="2"/>
       <c r="H249" s="3"/>
@@ -115948,7 +116538,7 @@
       <c r="AE249" s="3"/>
       <c r="AK249" s="5"/>
     </row>
-    <row r="250" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B250" s="1"/>
       <c r="E250" s="2"/>
       <c r="H250" s="3"/>
@@ -115958,14 +116548,14 @@
       <c r="X250" s="4"/>
       <c r="AK250" s="5"/>
     </row>
-    <row r="251" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B251" s="1"/>
       <c r="E251" s="2"/>
       <c r="G251" s="3"/>
       <c r="X251" s="4"/>
       <c r="AK251" s="5"/>
     </row>
-    <row r="252" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B252" s="1"/>
       <c r="E252" s="2"/>
       <c r="H252" s="3"/>
@@ -115978,7 +116568,7 @@
       <c r="AE252" s="3"/>
       <c r="AK252" s="5"/>
     </row>
-    <row r="253" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B253" s="1"/>
       <c r="E253" s="2"/>
       <c r="H253" s="3"/>
@@ -115990,7 +116580,7 @@
       <c r="AE253" s="3"/>
       <c r="AK253" s="5"/>
     </row>
-    <row r="254" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B254" s="1"/>
       <c r="E254" s="2"/>
       <c r="G254" s="3"/>
@@ -116003,7 +116593,7 @@
       <c r="AE254" s="3"/>
       <c r="AK254" s="5"/>
     </row>
-    <row r="255" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B255" s="1"/>
       <c r="E255" s="2"/>
       <c r="H255" s="3"/>
@@ -116017,7 +116607,7 @@
       <c r="AE255" s="3"/>
       <c r="AK255" s="5"/>
     </row>
-    <row r="256" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B256" s="1"/>
       <c r="E256" s="2"/>
       <c r="H256" s="3"/>
@@ -134398,7 +134988,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUBTOTAL(9,Planilha1!K1:K1825)</f>
-        <v>2040980.29</v>
+        <v>2123695.87</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -134413,7 +135003,7 @@
       </c>
       <c r="B4" s="9">
         <f>SUBTOTAL(9,Planilha1!L1:L1820)</f>
-        <v>337515.1100000001</v>
+        <v>350401.5500000001</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -134428,7 +135018,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUBTOTAL(9,Planilha1!M1:M1821)</f>
-        <v>3336458.1656944435</v>
+        <v>3436302.6425925922</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -134443,7 +135033,7 @@
       </c>
       <c r="B6" s="10">
         <f>SUBTOTAL(3,Planilha1!D2:D1821)</f>
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D6" t="s">
         <v>146</v>
@@ -134458,7 +135048,7 @@
       </c>
       <c r="B7" s="13">
         <f>B3/B6</f>
-        <v>8539.6664853556485</v>
+        <v>8632.9100406504076</v>
       </c>
       <c r="D7" t="s">
         <v>149</v>
@@ -134473,7 +135063,7 @@
       </c>
       <c r="B8" s="13">
         <f>B3/B4</f>
-        <v>6.0470782774732648</v>
+        <v>6.0607490748828008</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -134488,7 +135078,7 @@
       </c>
       <c r="B9" s="13">
         <f>B3/B5</f>
-        <v>0.61172062967413066</v>
+        <v>0.61801770416756197</v>
       </c>
       <c r="D9" t="s">
         <v>147</v>
